--- a/DSA_sheet.xlsx
+++ b/DSA_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFC5105-715E-4493-9477-BD34DF3F3222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56B220A6-206D-4C06-91F6-589426F56C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6E1FBF9E-BD98-4A07-9410-69C1E7B96CBE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="262">
   <si>
     <t>topic name</t>
   </si>
@@ -838,6 +838,30 @@
   </si>
   <si>
     <t>jun</t>
+  </si>
+  <si>
+    <t>SEARCHING</t>
+  </si>
+  <si>
+    <t>Linear Search</t>
+  </si>
+  <si>
+    <t>Binary Search</t>
+  </si>
+  <si>
+    <t>Ternary Search</t>
+  </si>
+  <si>
+    <t>Jump Search</t>
+  </si>
+  <si>
+    <t>Interpolation Search</t>
+  </si>
+  <si>
+    <t>Fibonacci Search</t>
+  </si>
+  <si>
+    <t>Exponential Search</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1031,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1045,6 +1069,7 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -16227,7 +16252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CCD79D-D2D1-430D-B13E-A60ED58471AF}">
-  <dimension ref="B3:L255"/>
+  <dimension ref="B3:L263"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.77734375" customWidth="1"/>
@@ -17815,6 +17840,50 @@
     <row r="255" spans="3:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="D255" s="8" t="s">
         <v>250</v>
+      </c>
+    </row>
+    <row r="257" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B257" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="D257" s="21" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="258" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D258" s="21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="259" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D259" s="21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="260" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D260" s="21" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="261" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D261" s="21" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="262" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D262" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="G262" s="9">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="263" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="D263" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="G263" s="9">
+        <v>46282</v>
       </c>
     </row>
   </sheetData>
@@ -18024,9 +18093,16 @@
     <hyperlink ref="D253" r:id="rId203" display="https://www.geeksforgeeks.org/dsa/minimum-number-of-bracket-reversals-needed-to-make-an-expression-balanced/" xr:uid="{CC9E97E1-7F07-4086-884C-2130170F9D11}"/>
     <hyperlink ref="D254" r:id="rId204" display="https://www.geeksforgeeks.org/dsa/word-wrap-problem-dp-19/" xr:uid="{B3B8F5BD-9103-449F-9953-1838451DEE39}"/>
     <hyperlink ref="D255" r:id="rId205" display="https://www.geeksforgeeks.org/dsa/decode-string-recursively-encoded-count-followed-substring/" xr:uid="{B2B83DD6-5598-47D6-A058-605246ED34F9}"/>
+    <hyperlink ref="D257" r:id="rId206" display="https://www.geeksforgeeks.org/dsa/linear-search/" xr:uid="{738F68CB-FEC5-437C-AFD5-6F98FE907B10}"/>
+    <hyperlink ref="D258" r:id="rId207" display="https://www.geeksforgeeks.org/dsa/binary-search/" xr:uid="{D79420B8-9C8D-45ED-8A7F-E226232662A5}"/>
+    <hyperlink ref="D259" r:id="rId208" display="https://www.geeksforgeeks.org/dsa/ternary-search/" xr:uid="{B6E3B683-A133-4990-83C5-6A16950DA584}"/>
+    <hyperlink ref="D260" r:id="rId209" display="https://www.geeksforgeeks.org/dsa/jump-search/" xr:uid="{F7CF3864-2B56-4A69-8DE3-C06946549F2E}"/>
+    <hyperlink ref="D261" r:id="rId210" display="https://www.geeksforgeeks.org/dsa/interpolation-search/" xr:uid="{314A1F85-CA10-41F3-8009-00648F926EF1}"/>
+    <hyperlink ref="D262" r:id="rId211" display="https://www.geeksforgeeks.org/dsa/fibonacci-search/" xr:uid="{D95377DF-86CB-405D-9055-C522003013AF}"/>
+    <hyperlink ref="D263" r:id="rId212" display="https://www.geeksforgeeks.org/dsa/exponential-search/" xr:uid="{3C214315-4DF4-4D64-8B12-1289D80B65F5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId206"/>
-  <drawing r:id="rId207"/>
+  <pageSetup orientation="portrait" r:id="rId213"/>
+  <drawing r:id="rId214"/>
 </worksheet>
 </file>